--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.79779503302954</v>
+        <v>9.3921416928673</v>
       </c>
       <c r="D2" t="n">
-        <v>27.06459984093199</v>
+        <v>4.397997474151449</v>
       </c>
       <c r="E2" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F2" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.89045121987951</v>
+        <v>4.53219832323042</v>
       </c>
       <c r="D3" t="n">
-        <v>4.927975068078664</v>
+        <v>0.800795948562783</v>
       </c>
       <c r="E3" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F3" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.4768729809166</v>
+        <v>9.177491859398947</v>
       </c>
       <c r="D4" t="n">
-        <v>57.38816857605389</v>
+        <v>9.325577393608757</v>
       </c>
       <c r="E4" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F4" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.58765176569363</v>
+        <v>2.370493411925215</v>
       </c>
       <c r="D5" t="n">
-        <v>15.74140015233538</v>
+        <v>2.557977524754499</v>
       </c>
       <c r="E5" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F5" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.07880034929944</v>
+        <v>2.775305056761159</v>
       </c>
       <c r="D6" t="n">
-        <v>16.986270384773</v>
+        <v>2.760268937525613</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F6" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.75067249835153</v>
+        <v>9.221984280982124</v>
       </c>
       <c r="D7" t="n">
-        <v>56.03805241230091</v>
+        <v>9.106183516998898</v>
       </c>
       <c r="E7" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F7" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.43615990742607</v>
+        <v>7.220875984956737</v>
       </c>
       <c r="D8" t="n">
-        <v>43.49838102167849</v>
+        <v>7.068486916022755</v>
       </c>
       <c r="E8" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F8" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.28139225864808</v>
+        <v>6.383226242030314</v>
       </c>
       <c r="D9" t="n">
-        <v>39.70201506221063</v>
+        <v>6.451577447609228</v>
       </c>
       <c r="E9" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F9" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.14294457887083</v>
+        <v>6.848228494066509</v>
       </c>
       <c r="D10" t="n">
-        <v>41.80011961705373</v>
+        <v>6.792519437771231</v>
       </c>
       <c r="E10" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F10" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.85054353473301</v>
+        <v>8.263213324394115</v>
       </c>
       <c r="D11" t="n">
-        <v>50.21951811795888</v>
+        <v>8.160671694168318</v>
       </c>
       <c r="E11" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F11" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.58545188611436</v>
+        <v>3.995135931493584</v>
       </c>
       <c r="D12" t="n">
-        <v>25.49509756796392</v>
+        <v>4.142953354794138</v>
       </c>
       <c r="E12" t="n">
-        <v>15.25772143569049</v>
+        <v>2.479379733299704</v>
       </c>
       <c r="F12" t="n">
-        <v>16.69414602081321</v>
+        <v>2.712798728382147</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
